--- a/testdata/result/누적강우/2025 70번 강우사상_누적강우.xlsx
+++ b/testdata/result/누적강우/2025 70번 강우사상_누적강우.xlsx
@@ -608,28 +608,28 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.4844157099723816</v>
+        <v>0.7933220863342285</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05172456055879593</v>
+        <v>0.01457122433930635</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1744047850370407</v>
+        <v>0.08332838863134384</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2274303422122825</v>
+        <v>0.1207113264748025</v>
       </c>
       <c r="V2" t="n">
-        <v>0.916182279586792</v>
+        <v>0.8922790288925171</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03870585560798645</v>
+        <v>0.0373898483812809</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1629230231046677</v>
+        <v>0.1438008844852448</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1967380380302357</v>
+        <v>0.1933645478914915</v>
       </c>
     </row>
     <row r="3">
@@ -2674,10 +2674,10 @@
         <v>13.427</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9570465087890625</v>
+        <v>0.9564741849899292</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.923452496528625</v>
+        <v>2.114423990249634</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         <v>13.939</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9691755175590515</v>
+        <v>0.9636703729629517</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.961983203887939</v>
+        <v>2.125836849212646</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         <v>14.488</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9834216237068176</v>
+        <v>0.9664385318756104</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.989666819572449</v>
+        <v>2.136416673660278</v>
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         <v>15.488</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9950032830238342</v>
+        <v>0.9864632487297058</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.020998239517212</v>
+        <v>2.276821374893188</v>
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         <v>16.61</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9997044801712036</v>
+        <v>1.044867038726807</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.058653831481934</v>
+        <v>2.38158106803894</v>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         <v>18.549</v>
       </c>
       <c r="P43" t="n">
-        <v>1.007591962814331</v>
+        <v>1.168918251991272</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.087503910064697</v>
+        <v>2.402264595031738</v>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         <v>22.878</v>
       </c>
       <c r="P44" t="n">
-        <v>1.017855167388916</v>
+        <v>1.283466458320618</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.14441990852356</v>
+        <v>2.412380695343018</v>
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         <v>26.841</v>
       </c>
       <c r="P45" t="n">
-        <v>1.036811232566833</v>
+        <v>1.374017715454102</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.187211036682129</v>
+        <v>2.419325828552246</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         <v>30.316</v>
       </c>
       <c r="P46" t="n">
-        <v>1.106001734733582</v>
+        <v>1.431421875953674</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.202521324157715</v>
+        <v>2.433712482452393</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3223,10 +3223,10 @@
         <v>33.95</v>
       </c>
       <c r="P47" t="n">
-        <v>1.18644642829895</v>
+        <v>1.468794226646423</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.239883661270142</v>
+        <v>2.500868082046509</v>
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         <v>39.414</v>
       </c>
       <c r="P48" t="n">
-        <v>1.284123420715332</v>
+        <v>1.485127449035645</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.281782388687134</v>
+        <v>2.59506893157959</v>
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         <v>41.573</v>
       </c>
       <c r="P49" t="n">
-        <v>1.373929500579834</v>
+        <v>1.485190868377686</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.372416257858276</v>
+        <v>2.670897006988525</v>
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
         <v>43.732</v>
       </c>
       <c r="P50" t="n">
-        <v>1.46757447719574</v>
+        <v>1.490282773971558</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.463098764419556</v>
+        <v>2.725795269012451</v>
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         <v>44.464</v>
       </c>
       <c r="P51" t="n">
-        <v>1.539481520652771</v>
+        <v>1.497457265853882</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.593832731246948</v>
+        <v>2.761234760284424</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         <v>46.501</v>
       </c>
       <c r="P52" t="n">
-        <v>1.576889157295227</v>
+        <v>1.528458714485168</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.77688455581665</v>
+        <v>2.774462699890137</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         <v>47.111</v>
       </c>
       <c r="P53" t="n">
-        <v>1.592720627784729</v>
+        <v>1.532832026481628</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.962027072906494</v>
+        <v>2.831665992736816</v>
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         <v>47.111</v>
       </c>
       <c r="P54" t="n">
-        <v>1.595736980438232</v>
+        <v>1.520761966705322</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.154994010925293</v>
+        <v>2.891837596893311</v>
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         <v>47.599</v>
       </c>
       <c r="P55" t="n">
-        <v>1.569285273551941</v>
+        <v>1.504926800727844</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.329385757446289</v>
+        <v>2.93795371055603</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3772,10 +3772,10 @@
         <v>47.66</v>
       </c>
       <c r="P56" t="n">
-        <v>1.532801747322083</v>
+        <v>1.48255467414856</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.449378490447998</v>
+        <v>2.982897758483887</v>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         <v>48.111</v>
       </c>
       <c r="P57" t="n">
-        <v>1.501394033432007</v>
+        <v>1.490581631660461</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.513344764709473</v>
+        <v>3.12983250617981</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
         <v>48.111</v>
       </c>
       <c r="P58" t="n">
-        <v>1.469593644142151</v>
+        <v>1.471503019332886</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.550246477127075</v>
+        <v>3.579218864440918</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         <v>49.88</v>
       </c>
       <c r="P59" t="n">
-        <v>1.436785340309143</v>
+        <v>1.554257988929749</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.534437417984009</v>
+        <v>3.823122978210449</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         <v>50.49</v>
       </c>
       <c r="P60" t="n">
-        <v>1.407051682472229</v>
+        <v>1.634755730628967</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.483952283859253</v>
+        <v>3.943036794662476</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         <v>50.49</v>
       </c>
       <c r="P61" t="n">
-        <v>1.375956296920776</v>
+        <v>1.691202521324158</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.411528587341309</v>
+        <v>3.989079475402832</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         <v>50.49</v>
       </c>
       <c r="P62" t="n">
-        <v>1.352843761444092</v>
+        <v>1.718768835067749</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.36283016204834</v>
+        <v>3.99177885055542</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         <v>50.49</v>
       </c>
       <c r="P63" t="n">
-        <v>1.335948705673218</v>
+        <v>1.723000764846802</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.305174350738525</v>
+        <v>3.966165065765381</v>
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         <v>50.49</v>
       </c>
       <c r="P64" t="n">
-        <v>1.31525731086731</v>
+        <v>1.710039854049683</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.232603788375854</v>
+        <v>3.92125415802002</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         <v>50.49</v>
       </c>
       <c r="P65" t="n">
-        <v>1.296048283576965</v>
+        <v>1.685286283493042</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.151957511901855</v>
+        <v>3.862689971923828</v>
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         <v>50.49</v>
       </c>
       <c r="P66" t="n">
-        <v>1.279471516609192</v>
+        <v>1.653091788291931</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.074997425079346</v>
+        <v>3.794136762619019</v>
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         <v>50.49</v>
       </c>
       <c r="P67" t="n">
-        <v>1.264674782752991</v>
+        <v>1.617061138153076</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.996890544891357</v>
+        <v>3.718619346618652</v>
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         <v>50.49</v>
       </c>
       <c r="P68" t="n">
-        <v>1.251581907272339</v>
+        <v>1.579580903053284</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.920104503631592</v>
+        <v>3.637903928756714</v>
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4565,10 +4565,10 @@
         <v>50.49</v>
       </c>
       <c r="P69" t="n">
-        <v>1.240076541900635</v>
+        <v>1.542675256729126</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.844396591186523</v>
+        <v>3.554001092910767</v>
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         <v>51.49</v>
       </c>
       <c r="P70" t="n">
-        <v>1.229638814926147</v>
+        <v>1.507447481155396</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.772013425827026</v>
+        <v>3.468502759933472</v>
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         <v>51.941</v>
       </c>
       <c r="P71" t="n">
-        <v>1.220379590988159</v>
+        <v>1.474412322044373</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.704910755157471</v>
+        <v>3.381665945053101</v>
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         <v>51.941</v>
       </c>
       <c r="P72" t="n">
-        <v>1.221475958824158</v>
+        <v>1.443649291992188</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.638732433319092</v>
+        <v>3.299629211425781</v>
       </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
@@ -4809,10 +4809,10 @@
         <v>51.941</v>
       </c>
       <c r="P73" t="n">
-        <v>1.227563619613647</v>
+        <v>1.429465413093567</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.572855949401855</v>
+        <v>3.223466396331787</v>
       </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
